--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0031.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0031.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Startorch Academy Anecdotes</t>
+          <t>Chuyện bên lề Học viện Startorch</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Startorch Academy Anecdotes</t>
+          <t>Chuyện bên lề Học viện Startorch</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Outpost Log</t>
+          <t>Nhật Ký Trạm Tiền Tiêu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Thông báo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Thông báo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The Last Glassful of Starfall</t>
+          <t>Ly Rượu Sao Rơi Cuối Cùng</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bols Blue in Sparkling Water</t>
+          <t>Bols Blue trong Nước Có Ga</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Her Beauty Outshines the Fireworks</t>
+          <t>Vẻ Đẹp Của Nàng Vượt Qua Cả Pháo Hoa</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Frostland Reavers' Throne</t>
+          <t>Ngai Vàng Cướp Biển Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Đến Nơi End Than Thở&lt;/i&gt;</t>
+          <t>&lt;i&gt;Đến Nơi Kết Thúc Than Thở&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Prophecy&lt;/i&gt;</t>
+          <t>&lt;i&gt;Lời Tiên Tri&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Letters of a Century&lt;/i&gt;</t>
+          <t>&lt;i&gt;Những lá thư của một thế kỷ&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The First Hunter&lt;/i&gt;</t>
+          <t>&lt;i&gt;Thợ Săn Đầu Tiên&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Scissorwoman&lt;/i&gt;</t>
+          <t>&lt;i&gt;Người Phụ Nữ Kéo&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Love Rumbles Like a Train&lt;/i&gt;</t>
+          <t>&lt;i&gt;Tình Yêu Rầm Rập Như Đoàn Tàu&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Specialty potions for wholesale</t>
+          <t>Thuốc Đặc Trị Bán Sỉ</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A knight in training</t>
+          <t>Một hiệp sĩ tập sự</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Sent bằng giọng nói</t>
+          <t>Đã gửi bằng giọng nói</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>I fold under mild pressure</t>
+          <t>Tôi chịu đựng áp lực kém lắm.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Working on it</t>
+          <t>Đang làm đây</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>A Boy's Notebook</t>
+          <t>Cuốn Sổ Của Một Cậu Bé</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Polar Nghiên cứu Outpost</t>
+          <t>Trạm Nghiên Cứu Vùng Cực</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>The Darkest Side of Startorch</t>
+          <t>Mặt Tối Nhất Của Ngôi Sao Khởi Đầu</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Faded Experiment Logs</t>
+          <t>Nhật ký thí nghiệm phai màu</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Faded Experiment Logs</t>
+          <t>Nhật ký thí nghiệm phai màu</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Faded Experiment Logs</t>
+          <t>Nhật ký thí nghiệm phai màu</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Anonymous Journal</t>
+          <t>Nhật ký ẩn danh</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Abandoned Journal</t>
+          <t>Nhật Ký Bị Bỏ Rơi</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Royan Runes Search Group</t>
+          <t>Nhóm Tìm Kiếm Rune Royan</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Please enter your text here</t>
+          <t>Vui lòng nhập văn bản của bạn tại đây</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Nhật Ký của Grand Commander</t>
+          <t>Nhật Ký của Đại Chỉ Huy</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Component Cache Log</t>
+          <t>Nhật Ký Bộ Nhớ Thành Phần</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Nhật ký</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Nhật ký</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Nhật ký</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Luuk Herssen's "Secret Workspace"</t>
+          <t>Góc "Làm việc bí mật" của Luuk Herssen</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ước Nguyện Trong Chuông</t>
+          <t>Điều Ước Trong Chuông</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Act V</t>
+          <t>Chương V</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Ánh Sao Từ Ngày Qua</t>
+          <t>Ánh Sao Ngày Xưa</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Ước Nguyện Trong Chuông: Hồi Kết</t>
+          <t>Điều Ước Trong Chuông: Đoạn Kết</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,8 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Dưới bầu trời đêm tan rã</t>
+          <t>Dưới Bầu Trời Đêm Tan Băng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5195,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>Xuyên thấu</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5335,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ancient Royan Incised Stone</t>
+          <t>Bia khắc cổ Royan</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5405,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>"Trích đoạn từ 'Song Cho Những Ký Ức'"</t>
+          <t>"Trích đoạn từ 'Khúc Ca Cho Những Ký Ức'"</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5475,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Lotta's Diary I</t>
+          <t>Nhật ký của Lotta I</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5545,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Lotta's Diary - II</t>
+          <t>Nhật ký của Lotta - II</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5615,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu Document</t>
+          <t>Tài liệu Viện Nghiên cứu</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5685,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Royan Rune Mark Point I</t>
+          <t>Điểm Đánh Dấu Rune Royan I</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5755,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Royan Rune Mark Point II</t>
+          <t>Điểm Đánh Dấu Rune Royan II</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5825,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Royan Rune Mark Point III</t>
+          <t>Điểm Đánh Dấu Rune Royan III</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5895,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Free Operative</t>
+          <t>Đặc Vụ Tự Do</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5965,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Free Operative</t>
+          <t>Đặc Vụ Tự Do</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6035,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Free Operative</t>
+          <t>Đặc Vụ Tự Do</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6595,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đội 4 &amp; Đội 9</t>
+          <t>Đội 4 và Đội 9</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7015,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Đội 3 &amp; Đội 5</t>
+          <t>Đội 3 và Đội 5</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7085,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>A Stack of Commission Letters</t>
+          <t>Một xấp thư nhiệm vụ</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7155,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Hóa đơn</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7225,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Denia's Birthday Memento</t>
+          <t>Kỷ vật sinh nhật Denia</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7295,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Denia's Birthday Memento</t>
+          <t>Kỷ vật sinh nhật Denia</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7505,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7575,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Featured Event</t>
+          <t>Sự Kiện Nổi Bật</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7645,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Recurring Event</t>
+          <t>Sự Kiện Lặp Lại</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7715,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Permanent Event</t>
+          <t>Sự kiện Vĩnh viễn</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7855,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Xác minh</t>
+          <t>Chiến Dịch Lollo: Xác Minh</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7925,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Xác minh</t>
+          <t>Chiến Dịch Lollo: Xác Minh</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7995,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Ngầu</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8065,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Stage Locked</t>
+          <t>Giai đoạn bị khóa</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8135,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8275,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8345,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Stars and Moon</t>
+          <t>Sao và Trăng</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8415,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Stars and Moon: Easy</t>
+          <t>Sao và Trăng: Dễ</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8485,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Stars and Moon: Thường</t>
+          <t>Sao và Trăng: Bình thường</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8555,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Stars and Moon: Difficult</t>
+          <t>Sao và Trăng: Khó</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8625,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>A Sunday in Riccioli</t>
+          <t>Một Ngày Chủ Nhật Ở Riccioli</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8695,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>A Sunday in Riccioli: Easy</t>
+          <t>Một ngày Chủ Nhật ở Riccioli: Dễ</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8765,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Một ngày Chủ Nhật ở Riccioli: Thường</t>
+          <t>Một ngày Chủ Nhật ở Riccioli: Bình thường</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8835,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>A Sunday in Riccioli: Difficult</t>
+          <t>Một Ngày Chủ Nhật Ở Riccioli: Khó Khăn</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8905,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Ragunna Memories</t>
+          <t>Ký Ức Ragunna</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8975,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Ragunna Memories: Easy</t>
+          <t>Ký Ức Ragunna: Dễ</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9045,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Ragunna Memories: Thường</t>
+          <t>Ký Ức Ragunna: Bình Thường</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9115,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ragunna Memories: Difficult</t>
+          <t>Ký Ức Ragunna: Khó</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9185,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Rừng Dawn</t>
+          <t>Rừng Bình Minh</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9255,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Rừng Dawn: Dễ</t>
+          <t>Rừng Bình Minh: Dễ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9325,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Rừng Dawn: Thường</t>
+          <t>Rừng Bình Minh: Bình thường</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9395,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Rừng Dawn: Khó</t>
+          <t>Rừng Bình Minh: Khó</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9465,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Windmill of Egla</t>
+          <t>Cối Xay Gió Egla</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9535,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Windmill of Egla: Easy</t>
+          <t>Cối Xay Gió Egla: Dễ</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9605,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Windmill of Egla: Bình Thường</t>
+          <t>Cối Xay Gió Egla: Bình Thường</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9675,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Windmill of Egla: Difficult</t>
+          <t>Cối Xay Gió Egla: Khó</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9745,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Water Lillies</t>
+          <t>Hoa Súng</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9815,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Water Lillies: Easy</t>
+          <t>Hoa Súng: Dễ</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9885,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Water Lillies: Thường</t>
+          <t>Hoa Súng: Bình thường</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9955,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Water Lillies: Difficult</t>
+          <t>Hoa Súng: Khó</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10025,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Dusk of Gold's Landing</t>
+          <t>Hoàng Hôn Của Bến Vàng</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10095,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Dusk of Gold's Landing: Easy</t>
+          <t>Hoàng Hôn Của Bến Vàng: Dễ</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10165,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Dusk of Gold's Landing: Bình Thường</t>
+          <t>Hoàng Hôn Của Bến Vàng: Bình Thường</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10235,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Dusk of Gold's Landing: Difficult</t>
+          <t>Hoàng Hôn Của Bến Vàng: Khó</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10375,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Oathbound Huntfire</t>
+          <t>Lửa Săn Được Thề</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10445,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Tro Tàn Của Glory</t>
+          <t>Tro Tàn Của Vinh Quang</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10515,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Scorching Irondust</t>
+          <t>Bụi Sắt Nóng Rực</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10585,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Cycle into Silence</t>
+          <t>Chu Kỳ Lặng Im</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10655,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Freeze Frame Camera</t>
+          <t>Camera Đóng Băng Khung Hình</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10725,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>The challenge has ended</t>
+          <t>Thử thách đã kết thúc</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10865,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Current Filter settings applied</t>
+          <t>Đã áp dụng bộ lọc hiện tại</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10935,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Color Temperature</t>
+          <t>Nhiệt Độ Màu</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11005,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Brightness</t>
+          <t>Ánh Sáng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11075,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Contrast</t>
+          <t>Tương Phản</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11145,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Saturation</t>
+          <t>Bão Hòa</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11215,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Grayscale</t>
+          <t>Thang Độ Xám</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11285,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Shadows</t>
+          <t>Những Bóng Đen</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11355,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Bloom</t>
+          <t>Nở Rộ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11425,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Vignette</t>
+          <t>Hồi Ảnh</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11495,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Sharpness</t>
+          <t>Sắc bén</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11565,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Film Grain</t>
+          <t>Hạt phim</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11705,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Quay lại Luck</t>
+          <t>Vận Đen</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11775,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Clean Sweep</t>
+          <t>Dọn Dẹp Sạch Sẽ</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11845,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Narrowly Lost</t>
+          <t>Thất Bại Sát Nút</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11915,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Narrowly Won</t>
+          <t>Thắng sát nút</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11985,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Bạn Lose</t>
+          <t>Ngươi Thua Rồi</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12055,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Bạn Thắng</t>
+          <t>Ngươi thắng rồi</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12125,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Play trò chơi với Jinhsi để mở khóa</t>
+          <t>Chơi trò chơi với Jinhsi để mở khóa</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12195,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Unlocked by default</t>
+          <t>Mở khóa mặc định</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12265,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Play trò chơi với Galbrena để mở khóa</t>
+          <t>Chơi trò chơi với Galbrena để mở khóa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12335,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Play all pairs</t>
+          <t>Đánh hết tất cả các đôi bài</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12545,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Do not use Instant Veto</t>
+          <t>Không sử dụng Phủ Quyết Tức Thời</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12685,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Do not use Instant Veto</t>
+          <t>Không sử dụng Phủ Quyết Tức Thời</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12825,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Quit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12895,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13105,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Insufficient Rice Dangos</t>
+          <t>Bánh Dango gạo không đủ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13175,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Item Locked</t>
+          <t>Vật phẩm bị khóa</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13245,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Item Unlocked</t>
+          <t>Vật phẩm đã mở khóa</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13315,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Không Information</t>
+          <t>Không có thông tin</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13385,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Try your luck</t>
+          <t>Thử vận may của cậu đi.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13525,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Insufficient Lollo Stamps</t>
+          <t>Không đủ Tem Lollo.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13595,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13735,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Vuốt sang trái để lột</t>
+          <t>Vuốt sang trái để lột bỏ</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13805,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Peel again</t>
+          <t>Lột lại lần nữa đi</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13945,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Độ khó</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14015,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tiếp tục xây dựng lại Spacetrek Observatory để mở khóa</t>
+          <t>Tiếp tục xây dựng lại Đài Thiên Văn Spacetrek để mở khóa</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14085,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14155,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Fallen Grave</t>
+          <t>Mộ Hoang Tàn</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14225,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Anima Cradle</t>
+          <t>Cái Nôi Sinh Mệnh</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14295,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Energy Hub</t>
+          <t>Trung Tâm Năng Lượng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14435,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Lumen Tower</t>
+          <t>Tháp Lumen</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14505,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Atilius Canyon</t>
+          <t>Hẻm Núi Atilius</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14575,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Hunter's Den</t>
+          <t>Hang ổ Thợ Săn</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14855,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Three Heroes' Crest</t>
+          <t>Ba Huy Hiệu Anh Hùng</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14925,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Honami Crossing</t>
+          <t>Ngã Tư Honami</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14995,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Harukaze Stadium</t>
+          <t>Sân vận động Harukaze</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15065,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Honami Central Park</t>
+          <t>Công Viên Trung Tâm Honami</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15135,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Hanakage Underground Street</t>
+          <t>Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15205,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Commercial District</t>
+          <t>Khu Thương mại</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15275,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15485,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Argentflare Drapes</t>
+          <t>Rèm Lửa Bạc</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15555,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15625,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15695,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Voidworm</t>
+          <t>Giun Voidworm</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15765,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15835,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Starward Riseway</t>
+          <t>Đại Lộ Sao Chổi</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15975,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Nightmare Revisited: Crimson Finale</t>
+          <t>Ác Mộng Trở Lại: Khúc Kết Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16045,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>The Lost Beyond</t>
+          <t>Vùng Đất Mất Tích</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16115,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Chaos</t>
+          <t>Hỗn Loạn</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16185,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16255,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16325,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16395,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16465,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16535,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16605,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Chế Độ Bẫy Chết</t>
+          <t>Chế Độ Bẫy Tử Thần</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16675,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Ephor's Palace</t>
+          <t>Cung Điện Ephor</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16745,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Weekly Challenge: Dark End</t>
+          <t>Thử Thách Hàng Tuần: Kết Cục Tăm Tối</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16885,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Neon Tower: Observation Deck</t>
+          <t>Tháp Neon: Đài Quan Sát</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16955,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Startorch Academy Departments</t>
+          <t>Các khoa của Học viện Startorch</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17025,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tactical Proving Grounds</t>
+          <t>Đấu Trường Chiến Thuật</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17095,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Etching Plains</t>
+          <t>Đồng Bằng Khắc Tạc</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17165,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Fangspire Chasm</t>
+          <t>Hẻm Núi Nanh Vuốt</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17235,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Collapsed Arcbend Ravine</t>
+          <t>Hẻm Núi Arcbend Sụp Đổ</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17305,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>The Heliodic Six</t>
+          <t>Lục Hạo Nhật</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17375,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu</t>
+          <t>Viện Nghiên cứu</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17445,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Exostrider's Reactor Drive</t>
+          <t>Bộ Phản Ứng Động cơ Exostrider</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17515,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Melody cuộc sống bất tận</t>
+          <t>Giai điệu cuộc sống bất tận</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17655,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Dawn Trên Bóng Tối Dâng Trào</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17795,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Tuyên ngôn Sinh viên Startorch Academy:</t>
+          <t>Tuyên ngôn Sinh viên Học viện Startorch:</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17865,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Where Moonlight Falls</t>
+          <t>Nơi Ánh Trăng Rơi</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17935,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Old Refuge</t>
+          <t>Nơi Ẩn Náu Xưa</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18005,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Neon Tower: Mê Cung Vòng Lặp</t>
+          <t>Tháp Neon: Mê Cung Vòng Lặp</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18075,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Cage of Memories</t>
+          <t>Lồng Ký Ức</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18145,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Peaceful Neighborhood</t>
+          <t>Khu phố yên bình</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18215,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Lament's Edge</t>
+          <t>Lưỡi Bi Ai</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18355,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Neon Tower: Base</t>
+          <t>Tháp Neon: Chân Tháp</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18425,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Neon Tower: Observation Deck</t>
+          <t>Tháp Neon: Đài Quan Sát</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18495,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Void Storm</t>
+          <t>Bão Hư Không</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18565,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Overclock I</t>
+          <t>Quá Tải I</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18635,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18775,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Reminiscence</t>
+          <t>Hồi ức</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18845,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Imperator</t>
+          <t>Đại Đế</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18915,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Dark Tide I</t>
+          <t>Thủy Triều Bóng Tối I</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18985,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Common Echo</t>
+          <t>Tiếng Vọng Thường</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19055,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>World of Sighs</t>
+          <t>Thế Giới Than Thở</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19125,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>New Solar Celebration</t>
+          <t>Lễ Hội Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19195,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>New Solar Celebration</t>
+          <t>Lễ Hội Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19265,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19335,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19405,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19475,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19545,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Perfect Honami</t>
+          <t>Honami Hoàn Hảo</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19615,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Genesis Nexus</t>
+          <t>Nexus Khởi Nguyên</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19755,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Tháng Mười</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19825,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Tháng Mười Một</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19895,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Giảm</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19965,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Tháng 2</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20105,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Thg 4</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20175,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Tháng Năm</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20385,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Tháng Tám</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20455,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Sept</t>
+          <t>Sept...</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20525,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Chính Trực</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20595,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20665,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Curiosity</t>
+          <t>Đồ Vật Kì Lạ</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20735,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Dedication</t>
+          <t>Sự Cống Hiến</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20805,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Passion</t>
+          <t>Đam Mê</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20875,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Humility</t>
+          <t>Khiêm nhường</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20945,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Compassion</t>
+          <t>Lòng trắc ẩn</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21015,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Tenacity</t>
+          <t>Kiên cường</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21085,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Kindness</t>
+          <t>Lòng tốt</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21155,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Wisdom</t>
+          <t>Trí Tuệ</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21225,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Commitment</t>
+          <t>Cam Kết</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21295,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Trách Nhiệm</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21365,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Sincerity</t>
+          <t>Chân Thành</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21435,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>Kỷ Luật</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21505,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Empathy</t>
+          <t>Sự đồng cảm</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21575,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Sự Điềm Tĩnh</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21645,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Khoan dung</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21715,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Introspection</t>
+          <t>Tự vấn</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21785,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>Sự sáng suốt</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21855,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Pragmatism</t>
+          <t>Thực dụng</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21925,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>New Moon's Blessing</t>
+          <t>Phước Lành Trăng Non</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21995,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t>Trăng Non</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22065,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Crescent Moon's Blessing</t>
+          <t>Phước Lành Của Trăng Lưỡi Liềm</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22135,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Crescent Moon</t>
+          <t>Trăng Lưỡi Liềm</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22205,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>First Quarter's Blessing</t>
+          <t>Phước lành của Trăng bán nguyệt</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22275,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>First Quarter</t>
+          <t>Trăng bán nguyệt đầu tiên</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22345,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Waxing Gibbous's Blessing</t>
+          <t>Phúc Lành Trăng Tròn Dần</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22415,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Waxing Gibbous</t>
+          <t>Trăng Tròn Dần</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22485,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Full Moon's Blessing</t>
+          <t>Phước Lành Của Trăng Tròn</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22555,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t>Trăng Tròn</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22625,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Waning Gibbous's Blessing</t>
+          <t>Phước Lành Trăng Khuyết Suy</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22695,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t>Trăng Khuyết Suy</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22765,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Last Quarter's Blessing</t>
+          <t>Phước Lành Trăng Khuyết Cuối</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22835,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Last Quarter</t>
+          <t>Trăng Khuyết Cuối</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22905,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Waning Crescent's Blessing</t>
+          <t>Phước Lành Trăng Khuyết Tàn</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22975,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t>Trăng Khuyết Tàn</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23045,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Twin Moons' Blessing</t>
+          <t>Phúc Lành Song Nguyệt</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23115,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Twin Moons</t>
+          <t>Song Nguyệt</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23185,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Rippled Moon's Blessing</t>
+          <t>Phước Lành Của Trăng Gợn Sóng</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23255,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Rippled Moon</t>
+          <t>Trăng Gợn Sóng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23325,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23535,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Crushmark</t>
+          <t>Dấu Hằn Tan Nát</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23605,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Rejuvenation</t>
+          <t>Sự Hồi Phục</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23675,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tất cả-Resonator Buffss</t>
+          <t>Buff Cho Tất Cả Resonator</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23745,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Void Storm Zone - Trường Lực Tăng Cường</t>
+          <t>Khu Vực Bão Hư Không - Trường Lực Tăng Cường</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23815,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23885,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23955,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24025,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24095,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24165,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24235,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>La~Ladiladiladila~Lalalaladida~</t>
+          <t>La~Li đà li đà la~La la la li đa~</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24305,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Lulala, Lululala, Lulala~</t>
+          <t>Lulala, lululala, lulala~</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24375,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Lulala, Lululala, Lulala~</t>
+          <t>Lulala, lululala, lulala~</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24445,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Lulala, Lululala, Lulala~</t>
+          <t>Lulala, lululala, lulala~</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24515,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Lulala, Lululala, Lulala~</t>
+          <t>Lulala, lululala, lulala~</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24655,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Bản nhạc chưa sử dụng trong Fabricatorium of the Deep</t>
+          <t>Bản nhạc chưa sử dụng trong Xưởng Dệt của Vực Sâu</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24795,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>피안의 진혼곡</t>
+          <t>"Khúc Tiễn Hồn Dưới Suối Vàng"</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24865,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Requiem of the Beyond</t>
+          <t>Khúc Ca Vượt Bờ</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24935,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>彼岸のレクイエム</t>
+          <t>Requiem Bên Kia Bờ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25005,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>彼岸的安魂曲</t>
+          <t>Khúc An Hồn Bên Kia</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25075,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>RUNNING FOR YOUR LIFE</t>
+          <t>CHẠY ĐỂ SỐNG CÒN</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25635,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Against the Tide</t>
+          <t>Chống Lại Dòng Chảy</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25775,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Everflow (EN) (EN)</t>
+          <t>Everflow</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25915,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Everflow (CN)</t>
+          <t>Dòng Chảy Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25985,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>바닷속 환상의 자장가</t>
+          <t>Khúc hát ru mộng ảo dưới biển sâu</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26055,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Elusive Seas</t>
+          <t>Biển Cả Mờ Ảo</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26125,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>沈む幻海</t>
+          <t>Ảo hải chìm sâu</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26195,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>沉沦幻海</t>
+          <t>Hải mộng chìm đắm</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26265,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>자유로운 영혼의왕 (자칭) (DESTINED)</t>
+          <t>Vị Vua của những linh hồn tự do (tự xưng) (DESTINED)</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>VUA CỦA NHỮNG LINH HỒN LẠC LỐI (TỰ XƯNG) (BUT ĐÃ ĐƯỢC ĐỊNH MỆNH)</t>
+          <t>VUA CỦA NHỮNG LINH HỒN LẠC LỐI (TỰ XƯNG) (NHƯNG ĐÃ ĐƯỢC ĐỊNH MỆNH)</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26405,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>自由気儘な魂が誇る愚者の王 (自任) (但し天命のキャプテン)</t>
+          <t>Kẻ tự xưng Vua của những kẻ ngốc – linh hồn tự do ngạo nghễ (nhưng thực chất là Đội trưởng của Vận Mệnh)</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26475,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>不羁灵魂之王 (虽然是自封) (但包的)</t>
+          <t>Vua Linh Hồn Phóng Túng (tự phong) (nhưng đúng thật)</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26545,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Daisy Crown (KR)</t>
+          <t>Vương Miện Cúc Dại (KR)</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26615,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Daisy Crown (EN)</t>
+          <t>Vương Miện Cúc Dại (EN)</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26685,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Daisy Crown (JP)</t>
+          <t>Vương Miện Cúc Dại (JP)</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26755,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Daisy Crown (CN)</t>
+          <t>Vương Miện Cúc Dại (CN)</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26825,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>ONE</t>
+          <t>MỘT</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26895,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Husk of Broken Dreams</t>
+          <t>Xác Thân Vỡ Mộng</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26965,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Sunken Elegy</t>
+          <t>Khúc Bi Ca Chìm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27035,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Radiance Across Sea and Sky</t>
+          <t>Ánh Sáng Trên Biển Trời</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27105,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>A Promised Moment</t>
+          <t>Khoảnh Khắc Đã Hứa</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27175,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Spacetrek Archive</t>
+          <t>Lưu Trữ Spacetrek</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27245,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Resonator Nursing Unit</t>
+          <t>Đơn Vị Điều Dưỡng Resonator</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27315,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Royan Market</t>
+          <t>Chợ Roya</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27385,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Culinary Station</t>
+          <t>Trạm Ẩm Thực</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27455,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Synth Armament Crafting Bay</t>
+          <t>Xưởng Chế Tạo Vũ Khí Tổng Hợp</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27525,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Không effect</t>
+          <t>Không có hiệu quả</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27875,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Dwarf Cassowary</t>
+          <t>Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28015,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28085,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28295,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28645,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28715,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -29135,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29345,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29415,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Voltscourge Stalker</t>
+          <t>Kẻ Rình Rập Sét Tàn Phá</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29625,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Vitreum Dancer</t>
+          <t>Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29835,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29905,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Hooscamp Flinger</t>
+          <t>Quái Hooscamp Ném Vật</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30045,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Galescourge Stalker</t>
+          <t>Thợ Săn Gale Scourge</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30185,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30255,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30325,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30675,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Diurnus Knight</t>
+          <t>Hiệp Sĩ Diurnus</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30885,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31025,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hocus Pocus</t>
+          <t>Ảo thuật biến!</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31235,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Nocturnus Knight</t>
+          <t>Hiệp Sĩ Nocturnus</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31795,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Luanquan</t>
+          <t>Loan Tuyền</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31865,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Lana</t>
+          <t>Lana.</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -32075,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Bream</t>
+          <t>Cá Bream</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32355,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Researcher Garcia</t>
+          <t>Nhà nghiên cứu Garcia</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32495,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hanolt</t>
+          <t>Ha-nốt</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32635,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>TARD-E Unit</t>
+          <t>Đơn vị TARD-E</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32775,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32845,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32915,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32985,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33195,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33405,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33475,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Rekindled Duel: Roya Frostlands</t>
+          <t>Trận Đấu Tái Sinh: Roya Frostlands</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33545,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Funding Battle</t>
+          <t>Chiến Tranh Tài Trợ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Funding Battle</t>
+          <t>Chiến Tranh Tài Trợ</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Funding Battle</t>
+          <t>Chiến Tranh Tài Trợ</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33755,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 11</t>
+          <t>Đạt Cấp Bậc 11</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33825,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 12</t>
+          <t>Đạt Cấp Bậc 12</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33895,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 13</t>
+          <t>Đạt Cấp Bậc 13</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33965,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 14</t>
+          <t>Đạt Cấp Bậc 14</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34035,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 15</t>
+          <t>Đạt Cấp Bậc 15</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -35295,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Reconstruction</t>
+          <t>Tái cấu trúc</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35435,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35505,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
